--- a/계산모델_엑셀/공정모델링_실험런시트_67런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_67런.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설계_설명" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase1_주효과_kV·R" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase2_재현성_F·W" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase3_교호작용" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase4_확인" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석_역설계모델" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1차실측" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase1_주효과_kV·R" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase2_재현성_F·W" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase3_교호작용" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase4_확인" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석_역설계모델" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -64,21 +70,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -446,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -462,147 +476,85 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>공정 모델링 실험 런시트 — 설계 설명 [67런 완전판]</t>
+          <t>공정 모델링 실험 런시트 — 설계 설명 [67런 완전판] (1차 실측 반영)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>대원칙: 정확한 검사결과가 최우선 제약. 시간단축은 '정확도를 지키는 범위 안에서만'(정확도를 시간과 바꾸지 않음).</t>
+          <t>대원칙: 정확한 검사결과가 최우선. 시간단축은 정확도 지키는 범위 안에서만. 자재=26µm·86µm(158µm 미보유→86µm 사용).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>★ 두 종류의 bump diameter: ①PD직경 D(독립·참값·자재고유) ②측정직경(종속·검사결과, 목표 Q_dia=100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>■ void% 기준 = 측정 bump면적(.csv: Area=π/4·측정직경²). 측정직경=PD(Q_dia100%)일 때만 성립 → kV 먼저.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>■ 1차 실측 교훈 (★설계 수정 근거 — '1차실측' 시트 참조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>· 86µm: 양호. kV*≈60.5(Q0.999), R스윕 안정. · 26µm: 미세 R일수록 과소측정·측정실패 (R0.2→Q0.57, R0.5→Q0.82). 원인=광자부족(얇은 범프+작은 픽셀→노이즈에 묻혀 어두운 핵만 잡음). → ①측정 가능 영역에서 kV* 찾기(26µm=R0.5·F32, kV55~58) ②미세 R은 높은 F와 짝(계단식) ③측정실패 조건에 런 배치 금지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8"/>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>■ 정확도 = void 총오차 ≤ 10% = √(픽셀화² + 노이즈²) ★</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>■ 정확도 = void 총오차 ≤ 10% = √(픽셀화² + 노이즈²)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>· 픽셀화(R): 2/N≤~7% → N_target≈29 · 노이즈(F,W): 2σ≤~7% → σ≤3.5%(F≥32). N=20은 노이즈 더하면 초과=부정확이라 폐기.</t>
+          <t>픽셀화(R):2/N≤7%→N≈29 / 노이즈(F,W):2σ≤7%. ★단 26µm은 미세 R이 측정을 깨서 N을 못 키움 → void 정확도가 물리적으로 ~13%(R0.5·N15) 수준에 묶일 수 있음. Phase의 R×F로 'F로 회복 가능한지' 확인.</t>
         </is>
       </c>
     </row>
     <row r="12"/>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>■ 정확도 사는 비용 순위: W(시간 공짜) &lt; F(1차) &lt; R(2차) ★핵심</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>SNR∝√(W·F·t), tact∝F/R². W 올리면 SNR↑인데 시간 안 늘어남(F는 프레임수라 시간 정비례, R은 2차). → 노이즈로 경계 흐리면 R 내리는 것보다 F(또는 두꺼운 범프면 W)로 경계 선명히 하는 게 싸고 효과적. 두꺼운 범프: W↑(공짜, 블러 한계까지)로 거친 R 허용. 26µm: R하한(0.2)+F하한(32)이라 F가 지렛대, 시간지렛대는 shot수.</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>■ 정확도 사는 비용 순위: W(시간 공짜) &lt; F(1차) &lt; R(2차). SNR∝√(W·F·t), tact∝F/R².</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>미세 R은 광자부족을 부르므로, 정확도는 R을 내리기보다 F(또는 두꺼운 범프면 W)로 사는 게 싸고 안전. 두꺼운/큰 범프: W↑(공짜)로 거친 R 허용. 26µm: R하한+측정한계라 F가 지렛대, 시간은 shot수.</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>■ 교호작용 설계 (Phase3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>R×F(26µm)</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>노이즈가 R효과 켜줌. 등시간쌍 (R0.25,F32)=(R0.5,F128)=tact512로 'R vs F' 직접비교</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>R×W(158µm)</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>W(공짜)로 거친 R 허용되나. (R3.0,W6)은 (R1.5,W4)보다 ~4배 빠름(W는 tact무관)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>W×F(158µm)</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>SNR∝√(W·F) 노이즈 교환</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>kV×F 가드(26µm)</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>가장자리 kV를 고F가 구제하나(매칭 강건성)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>kV×W 가드(158µm)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>투과 부족 kV에서 W가 소용있나</t>
-        </is>
-      </c>
-    </row>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>■ 교호작용(Phase3): R×F(26µm)·R×W(86µm)·W×F(86µm) + kV×F·kV×W 가드. 총오차_rel로 비교.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A15:H19"/>
-    <mergeCell ref="A4:H5"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="A7:H8"/>
+  <mergeCells count="8">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A17:H19"/>
+    <mergeCell ref="A15:H16"/>
+    <mergeCell ref="A11:H13"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="A11:H12"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="A5:H8"/>
+    <mergeCell ref="A21:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -614,12 +566,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1차 실측 데이터 (설계 수정의 근거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>86µm는 안정(kV*≈60.5). 26µm는 미세 R서 과소측정·실패(광자부족) → 측정 가능 영역/계단식 F로 재설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PD직경</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>측정직경</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Q_dia</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>kV1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>측정실패</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kV2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>과소측정(35%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>kV3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>86µm</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>86</v>
+      </c>
+      <c r="D7" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>kV4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>86µm</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>86</v>
+      </c>
+      <c r="D8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>미세R 과소</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>측정실패</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>F32+미세R</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>26µm</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>거친R가 더 정확</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>86µm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D12" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kV* 근처</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>86µm</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>86µm</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>86</v>
+      </c>
+      <c r="D14" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>void N8 과소</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -645,106 +1056,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R). gold=기준 앵커. N_target≈29. 고정 F32·W4.</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>kV 스윕은 측정되는 (R,F)에서(26µm=R0.5·F32, 86µm=R0.5·F32). R 스윕은 미세R에 高F 짝(계단식). gold=최정밀 측정점.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N≈29·R≥0.2·F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -765,10 +1176,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -797,7 +1208,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>측정직경=PD 되는 kV* 찾기</t>
+          <t>26µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -816,10 +1227,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>57.5</v>
+        <v>56.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -848,7 +1259,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>측정직경=PD 되는 kV* 찾기</t>
+          <t>26µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -867,10 +1278,10 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>59.5</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -899,7 +1310,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>측정직경=PD 되는 kV* 찾기</t>
+          <t>26µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -911,17 +1322,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D9" t="n">
         <v>58.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -950,7 +1361,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>158µm kV* 찾기</t>
+          <t>86µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -962,17 +1373,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D10" t="n">
         <v>60.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1001,7 +1412,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>158µm kV* 찾기</t>
+          <t>86µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1424,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>62.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1052,7 +1463,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>158µm kV* 찾기</t>
+          <t>86µm kV* 찾기(측정영역)</t>
         </is>
       </c>
     </row>
@@ -1071,10 +1482,10 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1103,7 +1514,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>N≈37 =gold</t>
+          <t>N≈15·F32</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1533,17 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
         <v/>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -1154,7 +1565,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>N≈29 =운영</t>
+          <t>N≈21·F64 (미세R=高F)</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1584,17 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
         <v/>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
@@ -1205,7 +1616,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>N≈15</t>
+          <t>N≈37·F128 (미세R=高F)</t>
         </is>
       </c>
     </row>
@@ -1217,17 +1628,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D15" t="n">
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -1256,7 +1667,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>N≈58 =gold</t>
+          <t>N≈49·F32</t>
         </is>
       </c>
     </row>
@@ -1268,17 +1679,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -1307,7 +1718,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>N≈30 =운영</t>
+          <t>N≈30·F32</t>
         </is>
       </c>
     </row>
@@ -1319,17 +1730,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D17" t="n">
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -1358,7 +1769,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>N≈15</t>
+          <t>N≈16·F32</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1382,7 +1793,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -1410,116 +1821,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>같은 범프 반복→void% σ. 총오차=√(편차²+(2σ)²)≤10%. 26µm=F스윕(R0.25·W4), 158µm=W스윕(R1.5·F32). F≥32.</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>같은 범프 반복→σ·총오차. 26µm=F스윕(R0.5, F로 측정회복+σ), 86µm=W스윕(R0.8; W가 86µm서 유효한지). kV*.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N≈29·R≥0.2·F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -1540,10 +1951,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -1572,7 +1983,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>F=32 재현성·총오차</t>
+          <t>F=32 재현성·측정회복</t>
         </is>
       </c>
       <c r="S6">
@@ -1599,10 +2010,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -1646,10 +2057,10 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -1693,10 +2104,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -1725,7 +2136,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>F=64 재현성·총오차</t>
+          <t>F=64 재현성·측정회복</t>
         </is>
       </c>
       <c r="S9">
@@ -1752,10 +2163,10 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1799,10 +2210,10 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1846,10 +2257,10 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1878,7 +2289,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>F=128 재현성·총오차</t>
+          <t>F=128 재현성·측정회복</t>
         </is>
       </c>
       <c r="S12">
@@ -1905,10 +2316,10 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1952,10 +2363,10 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1992,17 +2403,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D15" t="n">
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -2031,7 +2442,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>W=3 재현성·깜빡임</t>
+          <t>W=3 (86µm서 유효?)</t>
         </is>
       </c>
       <c r="S15">
@@ -2051,17 +2462,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -2098,17 +2509,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D17" t="n">
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -2145,17 +2556,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D18" t="n">
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -2184,7 +2595,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>W=4 재현성·깜빡임</t>
+          <t>W=4 (86µm서 유효?)</t>
         </is>
       </c>
       <c r="S18">
@@ -2204,17 +2615,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -2251,17 +2662,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D20" t="n">
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -2298,17 +2709,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D21" t="n">
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -2337,7 +2748,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>W=5 재현성·깜빡임</t>
+          <t>W=5 (86µm서 유효?)</t>
         </is>
       </c>
       <c r="S21">
@@ -2357,17 +2768,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D22" t="n">
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -2404,17 +2815,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D23" t="n">
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -2451,17 +2862,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D24" t="n">
         <v>60.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F24">
         <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
@@ -2490,7 +2901,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>W=6 재현성·깜빡임</t>
+          <t>W=6 (86µm서 유효?)</t>
         </is>
       </c>
       <c r="S24">
@@ -2510,17 +2921,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D25" t="n">
         <v>60.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F25">
         <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
@@ -2557,17 +2968,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D26" t="n">
         <v>60.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F26">
         <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
@@ -2605,7 +3016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2616,7 +3027,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -2644,116 +3055,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>R×F(26µm)·R×W(158µm)·W×F(158µm) 교환 + kV×F·kV×W 가드. tact∝F/R²(W무관). 총오차_rel로 비교.</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>R×F(26µm 광자부족 회복)·R×W(86µm)·W×F(86µm) + kV×F·kV×W 가드.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N≈29·R≥0.2·F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -2774,10 +3185,10 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -2806,7 +3217,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>R0.25×F32(N29) [등시간512]</t>
+          <t>R0.2×F32(N37)</t>
         </is>
       </c>
       <c r="S6">
@@ -2833,10 +3244,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -2880,10 +3291,10 @@
         <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -2912,7 +3323,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>R0.25×F128(N29)</t>
+          <t>R0.2×F128(N37) 미세+高F 회복?</t>
         </is>
       </c>
       <c r="S8">
@@ -2939,10 +3350,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -2986,7 +3397,7 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -3045,7 +3456,7 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
         <v>0.5</v>
@@ -3092,7 +3503,7 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E12" t="n">
         <v>0.5</v>
@@ -3124,7 +3535,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>R0.5×F128(N15) [등시간512]</t>
+          <t>R0.5×F128(N15)</t>
         </is>
       </c>
       <c r="S12">
@@ -3151,7 +3562,7 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -3191,17 +3602,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>60.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -3230,7 +3641,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>R1.5×W4(N30)</t>
+          <t>R0.8×W4(N30)</t>
         </is>
       </c>
       <c r="S14">
@@ -3250,17 +3661,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D15" t="n">
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -3297,17 +3708,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -3336,7 +3747,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>R1.5×W6(N30)</t>
+          <t>R0.8×W6(N30)</t>
         </is>
       </c>
       <c r="S16">
@@ -3356,17 +3767,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D17" t="n">
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -3403,17 +3814,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D18" t="n">
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -3442,7 +3853,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>R3.0×W4(N15)</t>
+          <t>R1.5×W4(N16)</t>
         </is>
       </c>
       <c r="S18">
@@ -3462,17 +3873,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -3509,17 +3920,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D20" t="n">
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -3548,7 +3959,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>R3.0×W6(N15) [거친R+고W=빠름]</t>
+          <t>R1.5×W6(N16) [거친R+高W=빠름]</t>
         </is>
       </c>
       <c r="S20">
@@ -3568,17 +3979,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D21" t="n">
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -3615,17 +4026,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D22" t="n">
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -3674,17 +4085,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D23" t="n">
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -3721,17 +4132,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D24" t="n">
         <v>60.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F24">
         <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
@@ -3780,17 +4191,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D25" t="n">
         <v>60.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F25">
         <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
@@ -3827,17 +4238,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D26" t="n">
         <v>60.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F26">
         <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
@@ -3886,17 +4297,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D27" t="n">
         <v>60.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F27">
         <f>IFERROR(ROUND(C27*0.2828/E27,0),"")</f>
@@ -3933,17 +4344,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
         <v>60.5</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F28">
         <f>IFERROR(ROUND(C28*0.2828/E28,0),"")</f>
@@ -3992,17 +4403,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
         <v>60.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F29">
         <f>IFERROR(ROUND(C29*0.2828/E29,0),"")</f>
@@ -4046,10 +4457,10 @@
         <v>26</v>
       </c>
       <c r="D30" t="n">
-        <v>59.5</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
         <f>IFERROR(ROUND(C30*0.2828/E30,0),"")</f>
@@ -4097,10 +4508,10 @@
         <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>59.5</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
         <f>IFERROR(ROUND(C31*0.2828/E31,0),"")</f>
@@ -4129,7 +4540,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>kV×F가드: 가장자리kV·F128 (고F가 구제?)</t>
+          <t>kV×F가드: 가장자리kV·F128 (구제?)</t>
         </is>
       </c>
     </row>
@@ -4141,17 +4552,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D32" t="n">
         <v>58.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F32">
         <f>IFERROR(ROUND(C32*0.2828/E32,0),"")</f>
@@ -4180,7 +4591,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>kV×W가드: 저투과kV·W4</t>
+          <t>kV×W가드: 저kV·W4</t>
         </is>
       </c>
     </row>
@@ -4192,17 +4603,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D33" t="n">
         <v>58.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="F33">
         <f>IFERROR(ROUND(C33*0.2828/E33,0),"")</f>
@@ -4231,7 +4642,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>kV×W가드: 저투과kV·W6 (W 소용?)</t>
+          <t>kV×W가드: 저kV·W6 (W 소용?)</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4255,7 +4666,7 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -4283,116 +4694,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; 총오차_rel≤10% &amp; tact 최소.</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>모델 산출로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; 총오차_rel≤10% &amp; tact 최소.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N≈29·R≥0.2·F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
+          <t>정확도=총오차≤10%. N≈29·R≥0.2·F≥32. 미세R은 高F와 짝(광자부족 회피). D=PD직경/측정직경=종속/void%=측정면적기준.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="11" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="11" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="11" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="11" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="11" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="T5" s="11" t="inlineStr">
         <is>
           <t>총오차_rel(자동)≤0.10</t>
         </is>
@@ -4414,12 +4825,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈56)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(모델R≈0.25)</t>
+          <t>(모델R,F짝)</t>
         </is>
       </c>
       <c r="F6">
@@ -4428,12 +4839,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>(모델F≥32)</t>
+          <t>(모델F)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(모델W4)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -4453,7 +4864,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>정확도(총오차≤10%) 확인</t>
+          <t>26µm 정확도 한계 확인(R×F 결과 반영)</t>
         </is>
       </c>
       <c r="S6">
@@ -4481,12 +4892,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈56)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(모델R≈0.25)</t>
+          <t>(모델R,F짝)</t>
         </is>
       </c>
       <c r="F7">
@@ -4495,12 +4906,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>(모델F≥32)</t>
+          <t>(모델F)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(모델W4)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -4536,12 +4947,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈56)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(모델R≈0.25)</t>
+          <t>(모델R,F짝)</t>
         </is>
       </c>
       <c r="F8">
@@ -4550,12 +4961,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>(모델F≥32)</t>
+          <t>(모델F)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(모델W4)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -4578,20 +4989,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C-158</t>
+          <t>C-86</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈60.5)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4610,7 +5021,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(모델W*)</t>
+          <t>(모델W)</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -4630,7 +5041,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>정확도 확인 (W↑로 R 거칠게 최적)</t>
+          <t>정확도 확인 (W로 R 거칠게 최적)</t>
         </is>
       </c>
       <c r="S9">
@@ -4645,20 +5056,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C-158</t>
+          <t>C-86</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈60.5)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4677,7 +5088,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(모델W*)</t>
+          <t>(모델W)</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -4700,20 +5111,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C-158</t>
+          <t>C-86</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>158µm</t>
+          <t>86µm</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(모델kV*)</t>
+          <t>(모델kV*≈60.5)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4732,7 +5143,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(모델W*)</t>
+          <t>(모델W)</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -4761,17 +5172,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -4783,177 +5194,138 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>역설계 모델 — 정확도(총오차≤10%) 만족 설정 중 최소 tact. R·F·W 함께 최적화</t>
+          <t>역설계 모델 — 측정 가능+정확도(총오차≤10%) 만족 설정 중 최소 tact</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>■ 확정 계수</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>■ 실측 반영 요점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>kV 직경식</t>
+          <t>26µm kV*</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>측정직경/PD=1+s·(kV−kV0). Phase1</t>
+          <t>≈56 (R0.5·F32서 스윕). 미세R서는 측정 자체가 깨져 kV* 못찾음</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>N_target</t>
+          <t>86µm kV*</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2/N≤~7%→N≈29. Phase1·2로 정밀화</t>
+          <t>≈60.5 (Q0.999). 안정</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>σ(F)</t>
+          <t>미세R 규칙</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Phase2: 2σ≤~7% 최소 F(≥32)</t>
+          <t>미세 R엔 高F 필수(광자부족→과소측정·실패). R×F로 회복폭 확정</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>R×F·R×W 교환</t>
+          <t>26µm 한계</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Phase3: 등시간에서 R↓ vs F↑ vs W↑ 어느게 정확한지 → 최적 (R,F,W)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>W*·블러</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Phase2·3: W 최적(블러 가드). W는 공짜라 두꺼운 범프 1순위</t>
+          <t>미세R 회복 안되면 R0.5(N15)·void정확도~13%가 물리 한계 — 수용 여부 결정 필요</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>kV 가드</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Phase3: kV*의 창이 F·W 충분할 때만 안전한지</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>■ 역설계 규칙</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tact</t>
+          <t>1) kV</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>a·(shot수·F)+b. W는 tact무관. 정확도 만족 집합서만 최소</t>
+          <t>측정되는 (R,F)에서 kV*(D) 트림→측정직경=PD(100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2) 정확도 순서</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>경계 흐리면: 86µm=W↑(공짜)→F↑ / 26µm=F↑ (R하한·측정한계)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>■ 역설계 규칙 (정확도 우선 → 그 안에서 시간최소)</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>3) R</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>정확도 남으면 R↑(2차, 비쌈)로 shot↓. 미세R 필요시 高F 동반</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>1) kV</t>
+          <t>4) 검증</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>kV*(D)서 1kV 트림→측정직경=PD(100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2) 정확도 확보 순서</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>경계 흐리면(노이즈 지배): 두꺼운범프=W↑(공짜, 블러까지)→F↑ / 26µm=F↑ (R은 하한)</t>
+          <t>측정성공 &amp; 총오차≤10% &amp; 매칭 &amp; Q_dia 후 tact</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>3) R</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>정확도 남으면 R↑(가장 비쌈, 2차)로 shot↓. R=max(0.2,D√p/N29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4) 검증</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>총오차≤10% &amp; 매칭 &amp; Q_dia 후 tact. 미달이면 W→F→R 순으로 보강</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>※ 정확도가 설정을 고정하면 시간여유 적어도 그대로(정확도&gt;시간). 확정 계수는 레시피모델·계산기에 반영.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>※ 확정 계수는 레시피모델·계산기에 반영. 26µm 정확도 한계는 데이터로 확정 후 tolerance 재검토.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B9:H9"/>
+  <mergeCells count="9">
     <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A15:H16"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A18:H19"/>
-    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B10:H10"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
